--- a/Quiz/Quiz-01/Excel/Table.xlsx
+++ b/Quiz/Quiz-01/Excel/Table.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\RIS_DATABASE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\database_lab\Quiz\Quiz-01\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A672243E-2A44-4359-A47C-ECF30F3BADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4575"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="58">
   <si>
     <t>1NF</t>
   </si>
@@ -192,12 +193,18 @@
   </si>
   <si>
     <t>3NF</t>
+  </si>
+  <si>
+    <t>Emerald Block</t>
+  </si>
+  <si>
+    <t>M006</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -520,31 +527,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:U30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="18.28515625" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="26.140625" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" customWidth="1"/>
-    <col min="13" max="13" width="20.42578125" customWidth="1"/>
-    <col min="14" max="14" width="20.140625" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" customWidth="1"/>
-    <col min="16" max="16" width="19.85546875" customWidth="1"/>
-    <col min="17" max="18" width="17.7109375" customWidth="1"/>
-    <col min="19" max="19" width="19.28515625" customWidth="1"/>
+    <col min="1" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" customWidth="1"/>
+    <col min="10" max="10" width="26.109375" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" customWidth="1"/>
+    <col min="13" max="13" width="20.44140625" customWidth="1"/>
+    <col min="14" max="14" width="20.109375" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" customWidth="1"/>
+    <col min="16" max="16" width="19.88671875" customWidth="1"/>
+    <col min="17" max="18" width="17.6640625" customWidth="1"/>
+    <col min="19" max="19" width="19.33203125" customWidth="1"/>
     <col min="20" max="21" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -552,7 +559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -593,12 +600,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="1">
-        <v>46025</v>
+        <v>46082</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -634,12 +641,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>46025</v>
+        <v>46082</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -663,7 +670,7 @@
         <v>27</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="K5" t="s">
         <v>29</v>
@@ -675,12 +682,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="1">
-        <v>46056</v>
+        <v>46083</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
@@ -716,7 +723,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -757,7 +764,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -798,12 +805,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="1">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="C9" t="s">
         <v>43</v>
@@ -839,12 +846,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>38</v>
       </c>
       <c r="B10" s="1">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
@@ -865,7 +872,7 @@
         <v>48</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J10" t="s">
         <v>52</v>
@@ -880,12 +887,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -932,12 +939,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
       <c r="B14" s="1">
-        <v>46025</v>
+        <v>46082</v>
       </c>
       <c r="D14" t="s">
         <v>1</v>
@@ -979,12 +986,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1</v>
       </c>
       <c r="B15" s="1">
-        <v>46025</v>
+        <v>46082</v>
       </c>
       <c r="D15" t="s">
         <v>1</v>
@@ -1026,12 +1033,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="1">
-        <v>46056</v>
+        <v>46083</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -1073,7 +1080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -1120,7 +1127,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1167,12 +1174,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>38</v>
       </c>
       <c r="B19" s="1">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="D19" t="s">
         <v>38</v>
@@ -1214,18 +1221,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>38</v>
       </c>
       <c r="B20" s="1">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="D20" t="s">
         <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="F20">
         <v>64</v>
@@ -1261,12 +1268,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1319,7 +1326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1354,7 +1361,7 @@
         <v>1</v>
       </c>
       <c r="O24" s="1">
-        <v>46025</v>
+        <v>46082</v>
       </c>
       <c r="P24" t="s">
         <v>15</v>
@@ -1372,7 +1379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -1407,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="1">
-        <v>46025</v>
+        <v>46082</v>
       </c>
       <c r="P25" t="s">
         <v>15</v>
@@ -1425,7 +1432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1460,7 +1467,7 @@
         <v>24</v>
       </c>
       <c r="O26" s="1">
-        <v>46056</v>
+        <v>46083</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
@@ -1478,7 +1485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -1531,7 +1538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -1584,7 +1591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -1619,7 +1626,7 @@
         <v>38</v>
       </c>
       <c r="O29" s="1">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="P29" t="s">
         <v>43</v>
@@ -1637,7 +1644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -1657,7 +1664,7 @@
         <v>48</v>
       </c>
       <c r="I30" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J30" t="s">
         <v>52</v>
@@ -1672,7 +1679,7 @@
         <v>38</v>
       </c>
       <c r="O30" s="1">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="P30" t="s">
         <v>43</v>
@@ -1692,27 +1699,27 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1"/>
-    <hyperlink ref="E5" r:id="rId2"/>
-    <hyperlink ref="E6" r:id="rId3"/>
-    <hyperlink ref="E7" r:id="rId4"/>
-    <hyperlink ref="E8" r:id="rId5"/>
-    <hyperlink ref="E9" r:id="rId6"/>
-    <hyperlink ref="E10" r:id="rId7"/>
-    <hyperlink ref="J14" r:id="rId8"/>
-    <hyperlink ref="J15" r:id="rId9"/>
-    <hyperlink ref="J16" r:id="rId10"/>
-    <hyperlink ref="J17" r:id="rId11"/>
-    <hyperlink ref="J18" r:id="rId12"/>
-    <hyperlink ref="J19" r:id="rId13"/>
-    <hyperlink ref="J20" r:id="rId14"/>
-    <hyperlink ref="C24" r:id="rId15"/>
-    <hyperlink ref="C25" r:id="rId16"/>
-    <hyperlink ref="C26" r:id="rId17"/>
-    <hyperlink ref="C27" r:id="rId18"/>
-    <hyperlink ref="C28" r:id="rId19"/>
-    <hyperlink ref="C29" r:id="rId20"/>
-    <hyperlink ref="C30" r:id="rId21"/>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="E9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="J14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="J15" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="J16" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="J17" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="J18" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="J19" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="J20" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C24" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="C25" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="C26" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C27" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="C28" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C29" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C30" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
